--- a/动态电量计算.xlsx
+++ b/动态电量计算.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>电网电能存量</t>
   </si>
@@ -34,43 +34,52 @@
     <t>EF01U9eE814EaOEA7Oa8</t>
   </si>
   <si>
+    <t>消耗速度</t>
+  </si>
+  <si>
+    <t>冗余</t>
+  </si>
+  <si>
+    <t>1/2速</t>
+  </si>
+  <si>
+    <t>EF01Oe4o1U3oAI3U9oe4</t>
+  </si>
+  <si>
+    <t>生产速度</t>
+  </si>
+  <si>
+    <t>终</t>
+  </si>
+  <si>
+    <t>EF01eaA5I9E564a4oAi8</t>
+  </si>
+  <si>
     <t>可达电量</t>
   </si>
   <si>
-    <t>冗余</t>
-  </si>
-  <si>
-    <t>1/2速</t>
-  </si>
-  <si>
-    <t>EF01Oe4o1U3oAI3U9oe4</t>
+    <t>药-紫-全</t>
+  </si>
+  <si>
+    <t>EF01ao6i437iuA95oe5e</t>
   </si>
   <si>
     <t>最低速度</t>
   </si>
   <si>
-    <t>终</t>
-  </si>
-  <si>
-    <t>EF01eaA5I9E564a4oAi8</t>
+    <t>电-紫-全</t>
+  </si>
+  <si>
+    <t>EF01o5u1AE01263OIieO</t>
   </si>
   <si>
     <t>推荐值</t>
   </si>
   <si>
-    <t>药-紫-全</t>
-  </si>
-  <si>
-    <t>EF01ao6i437iuA95oe5e</t>
-  </si>
-  <si>
     <t>掉电校验</t>
   </si>
   <si>
-    <t>电-紫-全</t>
-  </si>
-  <si>
-    <t>EF01o5u1AE01263OIieO</t>
+    <t>满电校验</t>
   </si>
   <si>
     <t>三分</t>
@@ -83,11 +92,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0&quot; 秒/个&quot;"/>
+    <numFmt numFmtId="177" formatCode="0\ &quot; 秒&quot;"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -779,7 +790,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -794,6 +805,10 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -801,7 +816,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1158,11 +1179,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="7.66666666666667" customWidth="1"/>
+    <col min="2" max="2" width="10.7777777777778" customWidth="1"/>
     <col min="3" max="3" width="12.8888888888889"/>
     <col min="4" max="4" width="11.8888888888889" customWidth="1"/>
     <col min="5" max="5" width="12.8888888888889"/>
@@ -1179,8 +1200,8 @@
         <v>1</v>
       </c>
       <c r="H1" s="1"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
@@ -1206,14 +1227,13 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
-        <f>ROUND(40*B2/B5,2)</f>
-        <v>50.93</v>
+      <c r="B3" s="4">
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="5">
         <v>50</v>
       </c>
       <c r="G3" t="s">
@@ -1227,9 +1247,8 @@
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <f>ROUND(40/(E2+E3)*B2,2)</f>
-        <v>880</v>
+      <c r="B4" s="4">
+        <v>2</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -1243,10 +1262,10 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <f t="array" ref="B5">MAX(IF((B9:L24&lt;=B4)*ISNUMBER(B9:L24),B9:L24))</f>
-        <v>864</v>
-      </c>
-      <c r="C5" s="5" t="str">
+        <f>ROUND(B3*B2/B7,2)</f>
+        <v>50.93</v>
+      </c>
+      <c r="C5" s="6" t="str">
         <f>IF((E2+E3)&gt;B2,"警告,需求+冗余已超过发电量，一个发电机已无法满足",IF((E2+E3)&lt;=0,"警告,需求+冗余要大于0",""))</f>
         <v/>
       </c>
@@ -1261,9 +1280,9 @@
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="6">
-        <f>1-((B5-40)*E2/B1)</f>
-        <v>1</v>
+      <c r="B6" s="7">
+        <f>ROUND(B3/(E2+E3)*B2,2)</f>
+        <v>880</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
@@ -1272,832 +1291,858 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" ht="15.15"/>
-    <row r="8" ht="15.15" spans="2:13">
-      <c r="B8" s="7">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7">
+        <f t="array" ref="B7">MAX(IF((B12:L27&lt;=B6)*ISNUMBER(B12:L27),B12:L27))</f>
+        <v>864</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="8">
+        <f>1-((B7-B3)*E2/B1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="9">
+        <f>ROUND(40-(B7-B3)*E2/(B2-E2),0)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" ht="15.15" spans="2:13">
+      <c r="B11" s="10">
         <v>0</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C11" s="11">
         <v>1</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D11" s="11">
         <v>2</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E11" s="11">
         <v>3</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F11" s="11">
         <v>4</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G11" s="11">
         <v>5</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H11" s="11">
         <v>6</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I11" s="11">
         <v>7</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J11" s="11">
         <v>8</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K11" s="11">
         <v>9</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L11" s="11">
         <v>10</v>
       </c>
-      <c r="M8" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="9">
+      <c r="M11" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="12">
         <v>0</v>
       </c>
-      <c r="B9">
-        <f t="shared" ref="B9:B24" si="0">2*3^B$8*2^$A9</f>
+      <c r="B12">
+        <f>$B$4*3^B$11*2^$A12</f>
         <v>2</v>
       </c>
-      <c r="C9">
-        <f t="shared" ref="C9:C24" si="1">2*3^C$8*2^$A9</f>
+      <c r="C12">
+        <f>$B$4*3^C$11*2^$A12</f>
         <v>6</v>
       </c>
-      <c r="D9">
-        <f t="shared" ref="D9:D24" si="2">2*3^D$8*2^$A9</f>
+      <c r="D12">
+        <f>$B$4*3^D$11*2^$A12</f>
         <v>18</v>
       </c>
-      <c r="E9">
-        <f t="shared" ref="E9:E24" si="3">2*3^E$8*2^$A9</f>
+      <c r="E12">
+        <f>$B$4*3^E$11*2^$A12</f>
         <v>54</v>
       </c>
-      <c r="F9">
-        <f t="shared" ref="F9:F24" si="4">2*3^F$8*2^$A9</f>
+      <c r="F12">
+        <f>$B$4*3^F$11*2^$A12</f>
         <v>162</v>
       </c>
-      <c r="G9">
-        <f t="shared" ref="G9:G24" si="5">2*3^G$8*2^$A9</f>
+      <c r="G12">
+        <f>$B$4*3^G$11*2^$A12</f>
         <v>486</v>
       </c>
-      <c r="H9">
-        <f t="shared" ref="H9:H24" si="6">2*3^H$8*2^$A9</f>
+      <c r="H12">
+        <f>$B$4*3^H$11*2^$A12</f>
         <v>1458</v>
       </c>
-      <c r="I9">
-        <f t="shared" ref="I9:I24" si="7">2*3^I$8*2^$A9</f>
+      <c r="I12">
+        <f>$B$4*3^I$11*2^$A12</f>
         <v>4374</v>
       </c>
-      <c r="J9">
-        <f t="shared" ref="J9:J24" si="8">2*3^J$8*2^$A9</f>
+      <c r="J12">
+        <f>$B$4*3^J$11*2^$A12</f>
         <v>13122</v>
       </c>
-      <c r="K9">
-        <f t="shared" ref="K9:K24" si="9">2*3^K$8*2^$A9</f>
+      <c r="K12">
+        <f>$B$4*3^K$11*2^$A12</f>
         <v>39366</v>
       </c>
-      <c r="L9">
-        <f t="shared" ref="L9:L24" si="10">2*3^L$8*2^$A9</f>
+      <c r="L12">
+        <f>$B$4*3^L$11*2^$A12</f>
         <v>118098</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="10">
+    <row r="13" spans="1:12">
+      <c r="A13" s="13">
         <v>1</v>
       </c>
-      <c r="B10">
-        <f t="shared" si="0"/>
+      <c r="B13">
+        <f>$B$4*3^B$11*2^$A13</f>
         <v>4</v>
       </c>
-      <c r="C10">
-        <f t="shared" si="1"/>
+      <c r="C13">
+        <f>$B$4*3^C$11*2^$A13</f>
         <v>12</v>
       </c>
-      <c r="D10">
-        <f t="shared" si="2"/>
+      <c r="D13">
+        <f>$B$4*3^D$11*2^$A13</f>
         <v>36</v>
       </c>
-      <c r="E10">
-        <f t="shared" si="3"/>
+      <c r="E13">
+        <f>$B$4*3^E$11*2^$A13</f>
         <v>108</v>
       </c>
-      <c r="F10">
-        <f t="shared" si="4"/>
+      <c r="F13">
+        <f>$B$4*3^F$11*2^$A13</f>
         <v>324</v>
       </c>
-      <c r="G10">
-        <f t="shared" si="5"/>
+      <c r="G13">
+        <f>$B$4*3^G$11*2^$A13</f>
         <v>972</v>
       </c>
-      <c r="H10">
-        <f t="shared" si="6"/>
+      <c r="H13">
+        <f>$B$4*3^H$11*2^$A13</f>
         <v>2916</v>
       </c>
-      <c r="I10">
-        <f t="shared" si="7"/>
+      <c r="I13">
+        <f>$B$4*3^I$11*2^$A13</f>
         <v>8748</v>
       </c>
-      <c r="J10">
-        <f t="shared" si="8"/>
+      <c r="J13">
+        <f>$B$4*3^J$11*2^$A13</f>
         <v>26244</v>
       </c>
-      <c r="K10">
-        <f t="shared" si="9"/>
+      <c r="K13">
+        <f>$B$4*3^K$11*2^$A13</f>
         <v>78732</v>
       </c>
-      <c r="L10">
-        <f t="shared" si="10"/>
+      <c r="L13">
+        <f>$B$4*3^L$11*2^$A13</f>
         <v>236196</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="10">
+    <row r="14" spans="1:12">
+      <c r="A14" s="13">
         <v>2</v>
       </c>
-      <c r="B11">
-        <f t="shared" si="0"/>
+      <c r="B14">
+        <f>$B$4*3^B$11*2^$A14</f>
         <v>8</v>
       </c>
-      <c r="C11">
-        <f t="shared" si="1"/>
+      <c r="C14">
+        <f>$B$4*3^C$11*2^$A14</f>
         <v>24</v>
       </c>
-      <c r="D11">
-        <f t="shared" si="2"/>
+      <c r="D14">
+        <f>$B$4*3^D$11*2^$A14</f>
         <v>72</v>
       </c>
-      <c r="E11">
-        <f t="shared" si="3"/>
+      <c r="E14">
+        <f>$B$4*3^E$11*2^$A14</f>
         <v>216</v>
       </c>
-      <c r="F11">
-        <f t="shared" si="4"/>
+      <c r="F14">
+        <f>$B$4*3^F$11*2^$A14</f>
         <v>648</v>
       </c>
-      <c r="G11">
-        <f t="shared" si="5"/>
+      <c r="G14">
+        <f>$B$4*3^G$11*2^$A14</f>
         <v>1944</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="6"/>
+      <c r="H14">
+        <f>$B$4*3^H$11*2^$A14</f>
         <v>5832</v>
       </c>
-      <c r="I11">
-        <f t="shared" si="7"/>
+      <c r="I14">
+        <f>$B$4*3^I$11*2^$A14</f>
         <v>17496</v>
       </c>
-      <c r="J11">
-        <f t="shared" si="8"/>
+      <c r="J14">
+        <f>$B$4*3^J$11*2^$A14</f>
         <v>52488</v>
       </c>
-      <c r="K11">
-        <f t="shared" si="9"/>
+      <c r="K14">
+        <f>$B$4*3^K$11*2^$A14</f>
         <v>157464</v>
       </c>
-      <c r="L11">
-        <f t="shared" si="10"/>
+      <c r="L14">
+        <f>$B$4*3^L$11*2^$A14</f>
         <v>472392</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="10">
+    <row r="15" spans="1:12">
+      <c r="A15" s="13">
         <v>3</v>
       </c>
-      <c r="B12">
-        <f t="shared" si="0"/>
+      <c r="B15">
+        <f>$B$4*3^B$11*2^$A15</f>
         <v>16</v>
       </c>
-      <c r="C12">
-        <f t="shared" si="1"/>
+      <c r="C15">
+        <f>$B$4*3^C$11*2^$A15</f>
         <v>48</v>
       </c>
-      <c r="D12">
-        <f t="shared" si="2"/>
+      <c r="D15">
+        <f>$B$4*3^D$11*2^$A15</f>
         <v>144</v>
       </c>
-      <c r="E12">
-        <f t="shared" si="3"/>
+      <c r="E15">
+        <f>$B$4*3^E$11*2^$A15</f>
         <v>432</v>
       </c>
-      <c r="F12">
-        <f t="shared" si="4"/>
+      <c r="F15">
+        <f>$B$4*3^F$11*2^$A15</f>
         <v>1296</v>
       </c>
-      <c r="G12">
-        <f t="shared" si="5"/>
+      <c r="G15">
+        <f>$B$4*3^G$11*2^$A15</f>
         <v>3888</v>
       </c>
-      <c r="H12">
-        <f t="shared" si="6"/>
+      <c r="H15">
+        <f>$B$4*3^H$11*2^$A15</f>
         <v>11664</v>
       </c>
-      <c r="I12">
-        <f t="shared" si="7"/>
+      <c r="I15">
+        <f>$B$4*3^I$11*2^$A15</f>
         <v>34992</v>
       </c>
-      <c r="J12">
-        <f t="shared" si="8"/>
+      <c r="J15">
+        <f>$B$4*3^J$11*2^$A15</f>
         <v>104976</v>
       </c>
-      <c r="K12">
-        <f t="shared" si="9"/>
+      <c r="K15">
+        <f>$B$4*3^K$11*2^$A15</f>
         <v>314928</v>
       </c>
-      <c r="L12">
-        <f t="shared" si="10"/>
+      <c r="L15">
+        <f>$B$4*3^L$11*2^$A15</f>
         <v>944784</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="10">
+    <row r="16" spans="1:12">
+      <c r="A16" s="13">
         <v>4</v>
       </c>
-      <c r="B13">
-        <f t="shared" si="0"/>
+      <c r="B16">
+        <f>$B$4*3^B$11*2^$A16</f>
         <v>32</v>
       </c>
-      <c r="C13">
-        <f t="shared" si="1"/>
+      <c r="C16">
+        <f>$B$4*3^C$11*2^$A16</f>
         <v>96</v>
       </c>
-      <c r="D13">
-        <f t="shared" si="2"/>
+      <c r="D16">
+        <f>$B$4*3^D$11*2^$A16</f>
         <v>288</v>
       </c>
-      <c r="E13">
-        <f t="shared" si="3"/>
+      <c r="E16">
+        <f>$B$4*3^E$11*2^$A16</f>
         <v>864</v>
       </c>
-      <c r="F13">
-        <f t="shared" si="4"/>
+      <c r="F16">
+        <f>$B$4*3^F$11*2^$A16</f>
         <v>2592</v>
       </c>
-      <c r="G13">
-        <f t="shared" si="5"/>
+      <c r="G16">
+        <f>$B$4*3^G$11*2^$A16</f>
         <v>7776</v>
       </c>
-      <c r="H13">
-        <f t="shared" si="6"/>
+      <c r="H16">
+        <f>$B$4*3^H$11*2^$A16</f>
         <v>23328</v>
       </c>
-      <c r="I13">
-        <f t="shared" si="7"/>
+      <c r="I16">
+        <f>$B$4*3^I$11*2^$A16</f>
         <v>69984</v>
       </c>
-      <c r="J13">
-        <f t="shared" si="8"/>
+      <c r="J16">
+        <f>$B$4*3^J$11*2^$A16</f>
         <v>209952</v>
       </c>
-      <c r="K13">
-        <f t="shared" si="9"/>
+      <c r="K16">
+        <f>$B$4*3^K$11*2^$A16</f>
         <v>629856</v>
       </c>
-      <c r="L13">
-        <f t="shared" si="10"/>
+      <c r="L16">
+        <f>$B$4*3^L$11*2^$A16</f>
         <v>1889568</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="10">
+    <row r="17" spans="1:12">
+      <c r="A17" s="13">
         <v>5</v>
       </c>
-      <c r="B14">
-        <f t="shared" si="0"/>
+      <c r="B17">
+        <f>$B$4*3^B$11*2^$A17</f>
         <v>64</v>
       </c>
-      <c r="C14">
-        <f t="shared" si="1"/>
+      <c r="C17">
+        <f>$B$4*3^C$11*2^$A17</f>
         <v>192</v>
       </c>
-      <c r="D14">
-        <f t="shared" si="2"/>
+      <c r="D17">
+        <f>$B$4*3^D$11*2^$A17</f>
         <v>576</v>
       </c>
-      <c r="E14">
-        <f t="shared" si="3"/>
+      <c r="E17">
+        <f>$B$4*3^E$11*2^$A17</f>
         <v>1728</v>
       </c>
-      <c r="F14">
-        <f t="shared" si="4"/>
+      <c r="F17">
+        <f>$B$4*3^F$11*2^$A17</f>
         <v>5184</v>
       </c>
-      <c r="G14">
-        <f t="shared" si="5"/>
+      <c r="G17">
+        <f>$B$4*3^G$11*2^$A17</f>
         <v>15552</v>
       </c>
-      <c r="H14">
-        <f t="shared" si="6"/>
+      <c r="H17">
+        <f>$B$4*3^H$11*2^$A17</f>
         <v>46656</v>
       </c>
-      <c r="I14">
-        <f t="shared" si="7"/>
+      <c r="I17">
+        <f>$B$4*3^I$11*2^$A17</f>
         <v>139968</v>
       </c>
-      <c r="J14">
-        <f t="shared" si="8"/>
+      <c r="J17">
+        <f>$B$4*3^J$11*2^$A17</f>
         <v>419904</v>
       </c>
-      <c r="K14">
-        <f t="shared" si="9"/>
+      <c r="K17">
+        <f>$B$4*3^K$11*2^$A17</f>
         <v>1259712</v>
       </c>
-      <c r="L14">
-        <f t="shared" si="10"/>
+      <c r="L17">
+        <f>$B$4*3^L$11*2^$A17</f>
         <v>3779136</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="10">
+    <row r="18" spans="1:12">
+      <c r="A18" s="13">
         <v>6</v>
       </c>
-      <c r="B15">
-        <f t="shared" si="0"/>
+      <c r="B18">
+        <f>$B$4*3^B$11*2^$A18</f>
         <v>128</v>
       </c>
-      <c r="C15">
-        <f t="shared" si="1"/>
+      <c r="C18">
+        <f>$B$4*3^C$11*2^$A18</f>
         <v>384</v>
       </c>
-      <c r="D15">
-        <f t="shared" si="2"/>
+      <c r="D18">
+        <f>$B$4*3^D$11*2^$A18</f>
         <v>1152</v>
       </c>
-      <c r="E15">
-        <f t="shared" si="3"/>
+      <c r="E18">
+        <f>$B$4*3^E$11*2^$A18</f>
         <v>3456</v>
       </c>
-      <c r="F15">
-        <f t="shared" si="4"/>
+      <c r="F18">
+        <f>$B$4*3^F$11*2^$A18</f>
         <v>10368</v>
       </c>
-      <c r="G15">
-        <f t="shared" si="5"/>
+      <c r="G18">
+        <f>$B$4*3^G$11*2^$A18</f>
         <v>31104</v>
       </c>
-      <c r="H15">
-        <f t="shared" si="6"/>
+      <c r="H18">
+        <f>$B$4*3^H$11*2^$A18</f>
         <v>93312</v>
       </c>
-      <c r="I15">
-        <f t="shared" si="7"/>
+      <c r="I18">
+        <f>$B$4*3^I$11*2^$A18</f>
         <v>279936</v>
       </c>
-      <c r="J15">
-        <f t="shared" si="8"/>
+      <c r="J18">
+        <f>$B$4*3^J$11*2^$A18</f>
         <v>839808</v>
       </c>
-      <c r="K15">
-        <f t="shared" si="9"/>
+      <c r="K18">
+        <f>$B$4*3^K$11*2^$A18</f>
         <v>2519424</v>
       </c>
-      <c r="L15">
-        <f t="shared" si="10"/>
+      <c r="L18">
+        <f>$B$4*3^L$11*2^$A18</f>
         <v>7558272</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="10">
+    <row r="19" spans="1:12">
+      <c r="A19" s="13">
         <v>7</v>
       </c>
-      <c r="B16">
-        <f t="shared" si="0"/>
+      <c r="B19">
+        <f>$B$4*3^B$11*2^$A19</f>
         <v>256</v>
       </c>
-      <c r="C16">
-        <f t="shared" si="1"/>
+      <c r="C19">
+        <f>$B$4*3^C$11*2^$A19</f>
         <v>768</v>
       </c>
-      <c r="D16">
-        <f t="shared" si="2"/>
+      <c r="D19">
+        <f>$B$4*3^D$11*2^$A19</f>
         <v>2304</v>
       </c>
-      <c r="E16">
-        <f t="shared" si="3"/>
+      <c r="E19">
+        <f>$B$4*3^E$11*2^$A19</f>
         <v>6912</v>
       </c>
-      <c r="F16">
-        <f t="shared" si="4"/>
+      <c r="F19">
+        <f>$B$4*3^F$11*2^$A19</f>
         <v>20736</v>
       </c>
-      <c r="G16">
-        <f t="shared" si="5"/>
+      <c r="G19">
+        <f>$B$4*3^G$11*2^$A19</f>
         <v>62208</v>
       </c>
-      <c r="H16">
-        <f t="shared" si="6"/>
+      <c r="H19">
+        <f>$B$4*3^H$11*2^$A19</f>
         <v>186624</v>
       </c>
-      <c r="I16">
-        <f t="shared" si="7"/>
+      <c r="I19">
+        <f>$B$4*3^I$11*2^$A19</f>
         <v>559872</v>
       </c>
-      <c r="J16">
-        <f t="shared" si="8"/>
+      <c r="J19">
+        <f>$B$4*3^J$11*2^$A19</f>
         <v>1679616</v>
       </c>
-      <c r="K16">
-        <f t="shared" si="9"/>
+      <c r="K19">
+        <f>$B$4*3^K$11*2^$A19</f>
         <v>5038848</v>
       </c>
-      <c r="L16">
-        <f t="shared" si="10"/>
+      <c r="L19">
+        <f>$B$4*3^L$11*2^$A19</f>
         <v>15116544</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="10">
+    <row r="20" spans="1:12">
+      <c r="A20" s="13">
         <v>8</v>
       </c>
-      <c r="B17">
-        <f t="shared" si="0"/>
+      <c r="B20">
+        <f>$B$4*3^B$11*2^$A20</f>
         <v>512</v>
       </c>
-      <c r="C17">
-        <f t="shared" si="1"/>
+      <c r="C20">
+        <f>$B$4*3^C$11*2^$A20</f>
         <v>1536</v>
       </c>
-      <c r="D17">
-        <f t="shared" si="2"/>
+      <c r="D20">
+        <f>$B$4*3^D$11*2^$A20</f>
         <v>4608</v>
       </c>
-      <c r="E17">
-        <f t="shared" si="3"/>
+      <c r="E20">
+        <f>$B$4*3^E$11*2^$A20</f>
         <v>13824</v>
       </c>
-      <c r="F17">
-        <f t="shared" si="4"/>
+      <c r="F20">
+        <f>$B$4*3^F$11*2^$A20</f>
         <v>41472</v>
       </c>
-      <c r="G17">
-        <f t="shared" si="5"/>
+      <c r="G20">
+        <f>$B$4*3^G$11*2^$A20</f>
         <v>124416</v>
       </c>
-      <c r="H17">
-        <f t="shared" si="6"/>
+      <c r="H20">
+        <f>$B$4*3^H$11*2^$A20</f>
         <v>373248</v>
       </c>
-      <c r="I17">
-        <f t="shared" si="7"/>
+      <c r="I20">
+        <f>$B$4*3^I$11*2^$A20</f>
         <v>1119744</v>
       </c>
-      <c r="J17">
-        <f t="shared" si="8"/>
+      <c r="J20">
+        <f>$B$4*3^J$11*2^$A20</f>
         <v>3359232</v>
       </c>
-      <c r="K17">
-        <f t="shared" si="9"/>
+      <c r="K20">
+        <f>$B$4*3^K$11*2^$A20</f>
         <v>10077696</v>
       </c>
-      <c r="L17">
-        <f t="shared" si="10"/>
+      <c r="L20">
+        <f>$B$4*3^L$11*2^$A20</f>
         <v>30233088</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="10">
+    <row r="21" spans="1:12">
+      <c r="A21" s="13">
         <v>9</v>
       </c>
-      <c r="B18">
-        <f t="shared" si="0"/>
+      <c r="B21">
+        <f>$B$4*3^B$11*2^$A21</f>
         <v>1024</v>
       </c>
-      <c r="C18">
-        <f t="shared" si="1"/>
+      <c r="C21">
+        <f>$B$4*3^C$11*2^$A21</f>
         <v>3072</v>
       </c>
-      <c r="D18">
-        <f t="shared" si="2"/>
+      <c r="D21">
+        <f>$B$4*3^D$11*2^$A21</f>
         <v>9216</v>
       </c>
-      <c r="E18">
-        <f t="shared" si="3"/>
+      <c r="E21">
+        <f>$B$4*3^E$11*2^$A21</f>
         <v>27648</v>
       </c>
-      <c r="F18">
-        <f t="shared" si="4"/>
+      <c r="F21">
+        <f>$B$4*3^F$11*2^$A21</f>
         <v>82944</v>
       </c>
-      <c r="G18">
-        <f t="shared" si="5"/>
+      <c r="G21">
+        <f>$B$4*3^G$11*2^$A21</f>
         <v>248832</v>
       </c>
-      <c r="H18">
-        <f t="shared" si="6"/>
+      <c r="H21">
+        <f>$B$4*3^H$11*2^$A21</f>
         <v>746496</v>
       </c>
-      <c r="I18">
-        <f t="shared" si="7"/>
+      <c r="I21">
+        <f>$B$4*3^I$11*2^$A21</f>
         <v>2239488</v>
       </c>
-      <c r="J18">
-        <f t="shared" si="8"/>
+      <c r="J21">
+        <f>$B$4*3^J$11*2^$A21</f>
         <v>6718464</v>
       </c>
-      <c r="K18">
-        <f t="shared" si="9"/>
+      <c r="K21">
+        <f>$B$4*3^K$11*2^$A21</f>
         <v>20155392</v>
       </c>
-      <c r="L18">
-        <f t="shared" si="10"/>
+      <c r="L21">
+        <f>$B$4*3^L$11*2^$A21</f>
         <v>60466176</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="10">
+    <row r="22" spans="1:12">
+      <c r="A22" s="13">
         <v>10</v>
       </c>
-      <c r="B19">
-        <f t="shared" si="0"/>
+      <c r="B22">
+        <f>$B$4*3^B$11*2^$A22</f>
         <v>2048</v>
       </c>
-      <c r="C19">
-        <f t="shared" si="1"/>
+      <c r="C22">
+        <f>$B$4*3^C$11*2^$A22</f>
         <v>6144</v>
       </c>
-      <c r="D19">
-        <f t="shared" si="2"/>
+      <c r="D22">
+        <f>$B$4*3^D$11*2^$A22</f>
         <v>18432</v>
       </c>
-      <c r="E19">
-        <f t="shared" si="3"/>
+      <c r="E22">
+        <f>$B$4*3^E$11*2^$A22</f>
         <v>55296</v>
       </c>
-      <c r="F19">
-        <f t="shared" si="4"/>
+      <c r="F22">
+        <f>$B$4*3^F$11*2^$A22</f>
         <v>165888</v>
       </c>
-      <c r="G19">
-        <f t="shared" si="5"/>
+      <c r="G22">
+        <f>$B$4*3^G$11*2^$A22</f>
         <v>497664</v>
       </c>
-      <c r="H19">
-        <f t="shared" si="6"/>
+      <c r="H22">
+        <f>$B$4*3^H$11*2^$A22</f>
         <v>1492992</v>
       </c>
-      <c r="I19">
-        <f t="shared" si="7"/>
+      <c r="I22">
+        <f>$B$4*3^I$11*2^$A22</f>
         <v>4478976</v>
       </c>
-      <c r="J19">
-        <f t="shared" si="8"/>
+      <c r="J22">
+        <f>$B$4*3^J$11*2^$A22</f>
         <v>13436928</v>
       </c>
-      <c r="K19">
-        <f t="shared" si="9"/>
+      <c r="K22">
+        <f>$B$4*3^K$11*2^$A22</f>
         <v>40310784</v>
       </c>
-      <c r="L19">
-        <f t="shared" si="10"/>
+      <c r="L22">
+        <f>$B$4*3^L$11*2^$A22</f>
         <v>120932352</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="10">
+    <row r="23" spans="1:12">
+      <c r="A23" s="13">
         <v>11</v>
       </c>
-      <c r="B20">
-        <f t="shared" si="0"/>
+      <c r="B23">
+        <f>$B$4*3^B$11*2^$A23</f>
         <v>4096</v>
       </c>
-      <c r="C20">
-        <f t="shared" si="1"/>
+      <c r="C23">
+        <f>$B$4*3^C$11*2^$A23</f>
         <v>12288</v>
       </c>
-      <c r="D20">
-        <f t="shared" si="2"/>
+      <c r="D23">
+        <f>$B$4*3^D$11*2^$A23</f>
         <v>36864</v>
       </c>
-      <c r="E20">
-        <f t="shared" si="3"/>
+      <c r="E23">
+        <f>$B$4*3^E$11*2^$A23</f>
         <v>110592</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="4"/>
+      <c r="F23">
+        <f>$B$4*3^F$11*2^$A23</f>
         <v>331776</v>
       </c>
-      <c r="G20">
-        <f t="shared" si="5"/>
+      <c r="G23">
+        <f>$B$4*3^G$11*2^$A23</f>
         <v>995328</v>
       </c>
-      <c r="H20">
-        <f t="shared" si="6"/>
+      <c r="H23">
+        <f>$B$4*3^H$11*2^$A23</f>
         <v>2985984</v>
       </c>
-      <c r="I20">
-        <f t="shared" si="7"/>
+      <c r="I23">
+        <f>$B$4*3^I$11*2^$A23</f>
         <v>8957952</v>
       </c>
-      <c r="J20">
-        <f t="shared" si="8"/>
+      <c r="J23">
+        <f>$B$4*3^J$11*2^$A23</f>
         <v>26873856</v>
       </c>
-      <c r="K20">
-        <f t="shared" si="9"/>
+      <c r="K23">
+        <f>$B$4*3^K$11*2^$A23</f>
         <v>80621568</v>
       </c>
-      <c r="L20">
-        <f t="shared" si="10"/>
+      <c r="L23">
+        <f>$B$4*3^L$11*2^$A23</f>
         <v>241864704</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="10">
+    <row r="24" spans="1:12">
+      <c r="A24" s="13">
         <v>12</v>
       </c>
-      <c r="B21">
-        <f t="shared" si="0"/>
+      <c r="B24">
+        <f>$B$4*3^B$11*2^$A24</f>
         <v>8192</v>
       </c>
-      <c r="C21">
-        <f t="shared" si="1"/>
+      <c r="C24">
+        <f>$B$4*3^C$11*2^$A24</f>
         <v>24576</v>
       </c>
-      <c r="D21">
-        <f t="shared" si="2"/>
+      <c r="D24">
+        <f>$B$4*3^D$11*2^$A24</f>
         <v>73728</v>
       </c>
-      <c r="E21">
-        <f t="shared" si="3"/>
+      <c r="E24">
+        <f>$B$4*3^E$11*2^$A24</f>
         <v>221184</v>
       </c>
-      <c r="F21">
-        <f t="shared" si="4"/>
+      <c r="F24">
+        <f>$B$4*3^F$11*2^$A24</f>
         <v>663552</v>
       </c>
-      <c r="G21">
-        <f t="shared" si="5"/>
+      <c r="G24">
+        <f>$B$4*3^G$11*2^$A24</f>
         <v>1990656</v>
       </c>
-      <c r="H21">
-        <f t="shared" si="6"/>
+      <c r="H24">
+        <f>$B$4*3^H$11*2^$A24</f>
         <v>5971968</v>
       </c>
-      <c r="I21">
-        <f t="shared" si="7"/>
+      <c r="I24">
+        <f>$B$4*3^I$11*2^$A24</f>
         <v>17915904</v>
       </c>
-      <c r="J21">
-        <f t="shared" si="8"/>
+      <c r="J24">
+        <f>$B$4*3^J$11*2^$A24</f>
         <v>53747712</v>
       </c>
-      <c r="K21">
-        <f t="shared" si="9"/>
+      <c r="K24">
+        <f>$B$4*3^K$11*2^$A24</f>
         <v>161243136</v>
       </c>
-      <c r="L21">
-        <f t="shared" si="10"/>
+      <c r="L24">
+        <f>$B$4*3^L$11*2^$A24</f>
         <v>483729408</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="10">
+    <row r="25" spans="1:12">
+      <c r="A25" s="13">
         <v>13</v>
       </c>
-      <c r="B22">
-        <f t="shared" si="0"/>
+      <c r="B25">
+        <f>$B$4*3^B$11*2^$A25</f>
         <v>16384</v>
       </c>
-      <c r="C22">
-        <f t="shared" si="1"/>
+      <c r="C25">
+        <f>$B$4*3^C$11*2^$A25</f>
         <v>49152</v>
       </c>
-      <c r="D22">
-        <f t="shared" si="2"/>
+      <c r="D25">
+        <f>$B$4*3^D$11*2^$A25</f>
         <v>147456</v>
       </c>
-      <c r="E22">
-        <f t="shared" si="3"/>
+      <c r="E25">
+        <f>$B$4*3^E$11*2^$A25</f>
         <v>442368</v>
       </c>
-      <c r="F22">
-        <f t="shared" si="4"/>
+      <c r="F25">
+        <f>$B$4*3^F$11*2^$A25</f>
         <v>1327104</v>
       </c>
-      <c r="G22">
-        <f t="shared" si="5"/>
+      <c r="G25">
+        <f>$B$4*3^G$11*2^$A25</f>
         <v>3981312</v>
       </c>
-      <c r="H22">
-        <f t="shared" si="6"/>
+      <c r="H25">
+        <f>$B$4*3^H$11*2^$A25</f>
         <v>11943936</v>
       </c>
-      <c r="I22">
-        <f t="shared" si="7"/>
+      <c r="I25">
+        <f>$B$4*3^I$11*2^$A25</f>
         <v>35831808</v>
       </c>
-      <c r="J22">
-        <f t="shared" si="8"/>
+      <c r="J25">
+        <f>$B$4*3^J$11*2^$A25</f>
         <v>107495424</v>
       </c>
-      <c r="K22">
-        <f t="shared" si="9"/>
+      <c r="K25">
+        <f>$B$4*3^K$11*2^$A25</f>
         <v>322486272</v>
       </c>
-      <c r="L22">
-        <f t="shared" si="10"/>
+      <c r="L25">
+        <f>$B$4*3^L$11*2^$A25</f>
         <v>967458816</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="10">
+    <row r="26" spans="1:12">
+      <c r="A26" s="13">
         <v>14</v>
       </c>
-      <c r="B23">
-        <f t="shared" si="0"/>
+      <c r="B26">
+        <f>$B$4*3^B$11*2^$A26</f>
         <v>32768</v>
       </c>
-      <c r="C23">
-        <f t="shared" si="1"/>
+      <c r="C26">
+        <f>$B$4*3^C$11*2^$A26</f>
         <v>98304</v>
       </c>
-      <c r="D23">
-        <f t="shared" si="2"/>
+      <c r="D26">
+        <f>$B$4*3^D$11*2^$A26</f>
         <v>294912</v>
       </c>
-      <c r="E23">
-        <f t="shared" si="3"/>
+      <c r="E26">
+        <f>$B$4*3^E$11*2^$A26</f>
         <v>884736</v>
       </c>
-      <c r="F23">
-        <f t="shared" si="4"/>
+      <c r="F26">
+        <f>$B$4*3^F$11*2^$A26</f>
         <v>2654208</v>
       </c>
-      <c r="G23">
-        <f t="shared" si="5"/>
+      <c r="G26">
+        <f>$B$4*3^G$11*2^$A26</f>
         <v>7962624</v>
       </c>
-      <c r="H23">
-        <f t="shared" si="6"/>
+      <c r="H26">
+        <f>$B$4*3^H$11*2^$A26</f>
         <v>23887872</v>
       </c>
-      <c r="I23">
-        <f t="shared" si="7"/>
+      <c r="I26">
+        <f>$B$4*3^I$11*2^$A26</f>
         <v>71663616</v>
       </c>
-      <c r="J23">
-        <f t="shared" si="8"/>
+      <c r="J26">
+        <f>$B$4*3^J$11*2^$A26</f>
         <v>214990848</v>
       </c>
-      <c r="K23">
-        <f t="shared" si="9"/>
+      <c r="K26">
+        <f>$B$4*3^K$11*2^$A26</f>
         <v>644972544</v>
       </c>
-      <c r="L23">
-        <f t="shared" si="10"/>
+      <c r="L26">
+        <f>$B$4*3^L$11*2^$A26</f>
         <v>1934917632</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="10">
+    <row r="27" spans="1:12">
+      <c r="A27" s="13">
         <v>15</v>
       </c>
-      <c r="B24">
-        <f t="shared" si="0"/>
+      <c r="B27">
+        <f>$B$4*3^B$11*2^$A27</f>
         <v>65536</v>
       </c>
-      <c r="C24">
-        <f t="shared" si="1"/>
+      <c r="C27">
+        <f>$B$4*3^C$11*2^$A27</f>
         <v>196608</v>
       </c>
-      <c r="D24">
-        <f t="shared" si="2"/>
+      <c r="D27">
+        <f>$B$4*3^D$11*2^$A27</f>
         <v>589824</v>
       </c>
-      <c r="E24">
-        <f t="shared" si="3"/>
+      <c r="E27">
+        <f>$B$4*3^E$11*2^$A27</f>
         <v>1769472</v>
       </c>
-      <c r="F24">
-        <f t="shared" si="4"/>
+      <c r="F27">
+        <f>$B$4*3^F$11*2^$A27</f>
         <v>5308416</v>
       </c>
-      <c r="G24">
-        <f t="shared" si="5"/>
+      <c r="G27">
+        <f>$B$4*3^G$11*2^$A27</f>
         <v>15925248</v>
       </c>
-      <c r="H24">
-        <f t="shared" si="6"/>
+      <c r="H27">
+        <f>$B$4*3^H$11*2^$A27</f>
         <v>47775744</v>
       </c>
-      <c r="I24">
-        <f t="shared" si="7"/>
+      <c r="I27">
+        <f>$B$4*3^I$11*2^$A27</f>
         <v>143327232</v>
       </c>
-      <c r="J24">
-        <f t="shared" si="8"/>
+      <c r="J27">
+        <f>$B$4*3^J$11*2^$A27</f>
         <v>429981696</v>
       </c>
-      <c r="K24">
-        <f t="shared" si="9"/>
+      <c r="K27">
+        <f>$B$4*3^K$11*2^$A27</f>
         <v>1289945088</v>
       </c>
-      <c r="L24">
-        <f t="shared" si="10"/>
+      <c r="L27">
+        <f>$B$4*3^L$11*2^$A27</f>
         <v>3869835264</v>
       </c>
     </row>
-    <row r="25" ht="15.15" spans="1:1">
-      <c r="A25" s="11" t="s">
-        <v>20</v>
+    <row r="28" ht="15.15" spans="1:1">
+      <c r="A28" s="14" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2105,13 +2150,13 @@
   <mergeCells count="1">
     <mergeCell ref="G1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B9:L24">
+  <conditionalFormatting sqref="B12:L27">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$B$5</formula>
+      <formula>$B$7</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="2" operator="notBetween">
-      <formula>40</formula>
-      <formula>$B$2*40</formula>
+      <formula>$B$3</formula>
+      <formula>$B$2*$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
